--- a/downloads/のあちゃん_noa_dayo2004_全ポスト.xlsx
+++ b/downloads/のあちゃん_noa_dayo2004_全ポスト.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全ポスト(時系列)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像付きのみ" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全ポスト(時系列)'!$A$1:$L$1409</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'画像付きのみ'!$A$1:$L$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1732,1586 +1730,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="533400" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="533400" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1076271" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="528637" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="719137" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="762000" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="647700" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="942975" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="533400" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="862012" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="762000" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="757237" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="638175" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="785812" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="719137" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="752475" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>30</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="533400" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="533400" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="533400" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1443037" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>46</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1253289" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>48</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="709612" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>51</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="709612" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>54</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="666750" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>55</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="714375" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>56</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="709612" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>57</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="709612" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>58</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="709612" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="709612" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1642241" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>61</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="590550" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="819150" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="709612" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -61618,3146 +60036,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L64"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>投稿日時(JST)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>いいね</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>リプ数</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>リポスト</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>閲覧数</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>画像枚数</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>画像URL</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>投稿URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="105" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>46243.93292824074</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>恥ずかしいけど初自撮りあげてみる🤭
-本当に容姿に自信ないからかわいいとかリプしてくれたら嬉しい💓💓💓
-初フォロワーさんと初リプさん早く現れないかな🥹</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>493</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPSJD_daAAA69ZV.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2086443233656389671</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="105" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>46243.96664351852</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>おやすみなさい🌙
-今日はフォロワーさん増えなかったけど、明日少しでも見てくれるといいな💓
-ちょっとだけ際どいの頑張ってみた🤭</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPSULKpaIAAzZHR.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2086455451206729752</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="105" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>46244.20938657408</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>おはよう☀️ 今日も仕事かぁ。月曜日って起きるだけでえらいよね🥲
-今週も頑張ろうね！</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>512</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPTkLfnbYAAmkmQ.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2086543417132433873</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="105" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>46246.54208333333</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>午後からも頑張ろうね💪</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>589</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPflAkDaEAAhCyw.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2087388760275333256</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="105" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>46246.54935185185</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>この前プール行った時の☀️
-ちょっとだけ露出多め？かな</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>652</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPfnaNyacAAhdvt.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2087391393581088873</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="105" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>46246.55520833333</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>いっぱいお話ししたい😚
-#裏アカ女子
-#おじさんと繋がりたい
-#おじさんすき
-#友達ほしい</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPfpVk1aAAARbXT.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2087393516624445949</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="105" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>46246.93907407407</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>一緒に寝る？🤭</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>753</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPhn27raoAAuXeJ.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2087532624793489635</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="105" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>46247.32776620371</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>おはのあ☀️
-今日は前言ってた通りちょっと小旅行🫶
-みんなは何するの〜？</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>694</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPjn9unawAAccQd.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2087673479273521448</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="105" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>46248.31292824074</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>車内で撮った足...ちょっとムチムチ？😓</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>796</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPosqexbYAA8OMm.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2088030490423165017</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="105" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>46248.32509259259</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>全然フォロワーさん増えない🥹
-やっぱり私可愛くないのかな...
-#裏アカ女子
-#おじさんと繋がりたい
-#おじさんすき
-#友達ほしい</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>1750</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPowrEQaMAABp_h.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2088034899714511164</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="105" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>46248.90853009259</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>全然映えないけど餃子を食べに宇都宮に😆
-意外とのあちゃん食いしん坊なのです😇</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>725</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPrw9ywb0AAD23u.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2088246331446055233</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="105" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>46248.93125</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>今日は横顔載せてみる🤭
-最近皆さんが褒めてくれるから自信が出てきた💪
-ありがとう🥹</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1261</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPr4dRtbgAAb-2m.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2088254563870777440</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="105" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>46249.51351851852</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>おはのあ☀️
-疲労が溜まってたのかお昼に起床😱
-今日も1日頑張ろうね🫶</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>839</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPu4Xb8acAApINw.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2088465568647286934</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="105" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>46249.94567129629</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>前載せた横顔が好評だったので🤭
-フォロー待ってます🫶
-#裏アカ女子
-#おじさんと繋がりたい
-#おじさんすき
-#友達ほしい
-#年上がすき</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>1028</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HPxGzY0bkAAWAqA.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2088622179286131153</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="105" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>46253.2716087963</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>おはのあ☀️
-みんなごめんね精神的に安定しなかった＋その後鬼の体調不良だった🥹
-今日からまたちゃんと投稿再開するからリプしてね😢</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQCO_z9agAAczdB.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2089827457490882716</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="105" customHeight="1">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>46253.89659722222</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>みんなのあの事好き？🫶</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>1493</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQFc_GebsAAGy7e.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2090053944852856878</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="105" customHeight="1">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>46255.02434027778</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>みんなは眠れない時なにする？🥱</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>929</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQLQrcKb0AARLla.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2090462626207969723</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="105" customHeight="1">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>46255.90049768519</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>今日は帰り道に急に雨降ってきて悲しかった🥹
-でも、のあは折り畳み傘常備してるんです😤😤😤
-みんな週末は何するの〜？</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>998</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQPxcxFboAEXiuj.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2090780133074641104</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="105" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>46256.89386574074</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>いつもと違う画角で撮ってみたり☁️
-彼女感？？みたいな感じ🤭</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>1636</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQU42vPaQAAoKVN.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091140119927681151</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="105" customHeight="1">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>46257.03730324074</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>フォロワーさん50人いったらこの動画出してみようかな！！！
-初の動画のあです😆恥ずかしいかも🫣</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1416</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQVoIWsa0AAzfRs.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091192099341586511</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="105" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>46257.375</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>おはのあ！！
-これは結構前に行った場所なんだけどわかるかな？？😌
-今日はみんな何するの？
-のあはお買い物に行きたい気持ち🥰</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>1284</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQWTOuKbEAA9V1e.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091314476788371736</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="105" customHeight="1">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>46257.81975694445</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>気づいたらフォロワーさん50人いってました🥳🥳🥳
-みんなのいいねやリプで毎日頑張れてます🥰これからもいっぱい投稿するのでいいねとかリプしてくれたら嬉しいな！</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>1544</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>https://video.twimg.com/amplify_video/2091475635051134976/vid/avc1/772x1206/-2lpPSHhMH098xpQ.mp4?tag=29 (動画)</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091475651652178136</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>46257.96697916667</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>最近、リプで「おはよう！」とか「かわいい！」とか送ってくれて実はかなり嬉しかった🥹
-X始める前は、自分のこと見たい人なんていないと思ってたから...
-実はX始めた理由、プロフィールに書いてること以外にもあったりするからフォロワーさん100人とか200人とか節目で話せたらな☺️</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>1877</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQaaiy9bMAAsTA2.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091529003614257436</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="105" customHeight="1">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>46258.43490740741</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>おはのあ☀️
-朝ってなんでこんなに幸せなんだろうね
-ぼーっとしてる時間が
-いちばん好きかも
-みんなは朝型？夜型？
-私は完全に夜型人間です🌙笑
-お仕事の人もお休みの人も
-今日も1日がんばろうねっ🔥
-よかったらリプで
-「おはよう」って送って？
-のあが元気になれるよ〜🥺💗
-#今日も1日がんばろう
-#寂しがり屋さんと繋がりたい
-#甘えさせてください</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>1418</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQc0xK_bAAAfPoo.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091698575063531732</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="105" customHeight="1">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>46258.50832175926</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>みんな月曜日だけど頑張れてますか❓
-のあはあと5日もあるのかぁ...ってなってる笑
-話変わるんだけど、もっと自撮り上手くなりたい！可愛く撮りたい！って思うからみんながこういう自撮り撮ってよとかこういう服装がいいとかあったらリプでリクエストしてみてね🥳
-#年上好き
-#裏アカ女子
-#自撮り
-#清楚系</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>1220</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQdMtkcbMAAoOTk.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091725176639750651</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="105" customHeight="1">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>46258.78140046296</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>なんか夜になると
-急に誰かと話したくなるのなんでだろ🥺
-隣空いてるけど、来る？笑
-寝るまでちょっとお話しよ？
-今日あったこと、のあに1個だけ教えて🤍</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>2031</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQem9yybYAAOfrj.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2091824138625409178</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="105" customHeight="1">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>46259.54825231482</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>おひる〜☀️
-朝バタバタしてて投稿できなかった💦
-午前中がんばったから
-そろそろ褒めてもらってもいい時間？🥺笑
-午後も頑張れるように
-のあに一言くださいっ
-全部ちゃんと読みにいくからね👀🤍</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>1585</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQijtk-acAA0rM_.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2092102034594095363</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="105" customHeight="1">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>46259.96766203704</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>のあちゃんちょっとだけ体調...悪いかも？
-最近クーラー直当たりで喉の調子が悪い🥹
-みんなは体調大丈夫？</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>1433</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQkt8usawAAbn15.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2092254027253940252</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="105" customHeight="1">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>46260.40754629629</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>おはよ〜☀️
-朝起きて隣にのあいたら
-最初になんて言う？👀🤍
-今日もお仕事の人もお休みの人も
-のあと一緒にがんばろ〜！
-とりあえず「おはよ」だけでも
-言いにきてくれたら嬉しい🥺</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>1701</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQm-7gFaQAAEkKw.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2092413435053215889</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="105" customHeight="1">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>46261.4371875</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>おはよ〜☀️
-今日はちょっとメガネのあ👓🤍
-コーヒー買って会社いってきます☕️
-ねえ、メガネありとなし
-どっちののあが好き？🥺
-朝から褒めてもらえたら
-今日一日がんばれる気がする…笑
-お仕事の人、一緒にがんばろ〜！
-お休みの人はのあの分までゆっくりしてね🫶</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQsSRvPaAAA1jr0.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2092786561721282897</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="105" customHeight="1">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>46261.95065972222</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>ただいま〜🌙
-今日も1日おつかれさまっ
-外ではちゃんとしてるけど
-家帰った瞬間こんな感じです🥺笑
-ねえ、今日くらい
-のあに甘えてもいいんだよ？
-今日がんばったこと1個だけ教えて？
-のあが褒めます🥰</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>1688</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQu7hXfagAAQhRu.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2092972641456189524</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="105" customHeight="1">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>46262.91334490741</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>鏡の前からこんばんは🪞🤍
-今日はもう完全にオフモードです🥺
-このあと一緒に過ごせるなら
-なにする？
-のあはソファでくっつきながら
-くだらない話してたいかも…笑
-寝る前にちょっとだけ構って？🫶</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>2832</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQz40LbakAAD1bL.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2093321506235539826</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="105" customHeight="1">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>46263.95901620371</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>今日も会いにきてくれてありがとう🌙🤍
-最近、毎日のようにリプくれる人とか
-名前覚えてきた人が少しずつ増えてきて
-実はけっこう嬉しい🥺
-そこで寝る前にひとつだけ聞きたいっ
-のあのどんなところが好き？
-「写真」「雰囲気」「話し方」とか
-一言だけでもいいから教えてほしい👀
-いつも見てるだけの人も
-今日だけは初リプしてくれたら嬉しいな🤍
-ちゃんと全部読みにいくね。
-おやすみ前に少しお話しよ〜🌙</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>2140</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HQ5RdVWaQAACyDM.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2093700445135155623</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="105" customHeight="1">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>46266.69414351852</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>ただいま〜🥺
-少しの間Xから消えてました…笑
-凄く忙しかったの...ごめんなさい🥹
-のあのこと忘れてない？
-ちょっとだけ
-「最近見ないな」って思ってくれてた人いたら
-正直にリプして？👀🤍</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>2382</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HRHW7TRawAAKl5W.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2094691619710918693</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="105" customHeight="1">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>46267.6829050926</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>昨日ただいまってしたら
-「待ってた」って言ってくれる人いて
-思ってたより嬉しかった🥺🤍
-2日いなかった分、今日はいっぱい話したい。
-ねえ、みんなって
-いつ頃からのあのこと見てくれてるの？👀
-最近見つけてくれた人も
-ずっといるよって人も教えてほしいっ</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>2433</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HRMc0ChaIAAVNNJ.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2095049936664756424</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="105" customHeight="1">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>46268.80282407408</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>今日もおつかれさま〜🌙
-帰り道にちょっとだけ📸
-最近リプで名前見ると
-「今日も来てくれた」って思う人が増えてきた🥺
-意外とちゃんと覚えてるんだよ？笑
-ねえ、もし毎日ひとつだけ
-のあから届くならどれがいい？👀
-① おはよう
-② おつかれさま
-③ おやすみ
-番号だけでも教えて🤍
-ちなみに毎日来てくれる人は
-もっと覚えちゃうかも</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>2520</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HRSN7XdaYAAebFV.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2095455782326382942</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="105" customHeight="1">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>46269.9562037037</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>夜のカフェってなんか好き。
-ぼーっとしながら今日あったこと話したくなる🥺
-もし今ここに一緒にいたら
-今日あったこと、何から話してくれる？
-嬉しかったことでも愚痴でもなんでも聞くよ👀
-最近みんなのこと
-リプで少しずつ知れてるの結構うれしい。
-今日ものあに1個だけ教えて？🤍</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>2667</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HRYKEX-aUAAjYiN.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2095873751145730471</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="105" customHeight="1">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>46269.97125</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>金曜日までたどり着いたみんなへ🌙
-今週もほんとにおつかれさま🤍
-仕事しんどかった人も
-学校がんばった人も
-なんとか1週間乗り切った人も、みんなえらいっ！
-そんな頑張った人に
-のあからご褒美です🫣🤍
-今日はもう何も考えずにゆっくりしよ？
-ご褒美受け取った人は
-「受け取った」ってリプしてね👀
-一人ずつ「おつかれさま」言いにいくっ🫶</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>2934</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HRYPB2ibEAIDatF.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2095879205682819476</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="105" customHeight="1">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>46276.51115740741</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>ただいま〜🥺🤍
-気づいたら6日もいなくなってた…
-さすがに忘れられてないよね？笑
-まだのあのこと覚えてる人、
-「おかえり」って言ってほしいな🫣
-久しぶりにみんなの名前見たいっ
-今日からまた仲良くしてね🤍</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>3303</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HR56g6JbIAAJerN.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2098249186210971669</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="105" customHeight="1">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>46282.82274305556</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>最近雨の日多かったよね😢
-今日はちょっとだけ寄り道して帰りますっ
-みんなはもうお仕事終わった？👀
-まだ頑張ってる人は、のあが応援する📣
-今日も1日おつかれさま🫶
-帰ったら何して過ごすか教えて〜</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>3575</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HSaav_VakAEtIEx.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2100536430166720864</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="105" customHeight="1">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>46296.48556712963</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>おはのあ🪴
-今日からまたポストしていくねん🙂‍↕️
-えっくす離れてる間に実は私、                                                                                                                                                                                                             
-インフルかかってました😭
-一人暮らしのインフルってつらたん🥺︎
-なんで看病来てくれなかったの？
-寂しかったよ～
-こういう時に付きっきりで看病してくれる優しい人欲しい😇
-立候補してくれる人いますか？</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>4036</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HTgxQF8a4AAcAQg.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2105487670202028426</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="105" customHeight="1">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>46296.82048611111</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>カミングアウトなんだけど…
-もうちょっと焦らすことにします🫣
-相変わらず人見知りだしコミュ障なんだけど、最近ひとりでまた〇〇ッ〇に行くのにハマってて笑
-この手の動きなんだけど、わかる人いる？🥹
-正解したら君のボタンもポチッとしちゃおっかな🙈💕︎
-💡ヒント💡                           
-プロフィール👀</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>5020</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>https://video.twimg.com/amplify_video/2105608839374794752/vid/avc1/720x1280/i3v933tP8W91KoaO.mp4?tag=29 (動画)</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2105609042953691330</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="105" customHeight="1">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>46297.39445601852</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>華金だしフィーバーしたい気分🙈
-誰か私のボタンポチッと押してみませんか☝️🆘？</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>5340</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HTldMcsbcAEwKpM.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2105817041257316434</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="105" customHeight="1">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>46297.79418981481</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>️⭕️パチスロ女子の良いところ
-・夢追いロマンチスト
-・昔のアニメに何故か詳しい
-・目押しで動体視力を鍛えている
-・休日は早起きで健康的
-・予算内でのヤリクリが上手
-・玉と棒とポッチの扱いが上手い
-❌パチスロ女子の悪いところ⬇</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>5968</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HTnY_7kbwAIrZWX.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2105961898139414753</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="105" customHeight="1">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>46298.44703703704</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>あなたはどっち派？
-①🥧🤏
-②🫴🍑
-私は…                                                                                                                                                                                                                                                
-どっちも派🙋‍♀️</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>6635</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HTq2g7ZaYAAZIG4.jpg?name=orig
-https://pbs.twimg.com/media/HTq2g56b0AAL2Ci.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2106198483892130157</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="105" customHeight="1">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>46298.8134375</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>【のあちゃんクイズ🎰】
-のあの理想の休日デートの1日の流れを順番通りに並び替えてね💡
-①腹ごなしに夜散歩👭
-②朝の勢いで🍌💦
-②パチ屋で並び打ち🎰
-③2度寝からのセッ🙈💕︎
-④お昼は町中華🥟
-④勝利の焼肉🥩🔥
-⑤吸い込まれるように🏩へ…
-こんな休日が好きな人と過ごせたら最高🥹でも、        
-こんなムッツリ人見知りコミュ障パチンカスをもらってくれる人なかなかいなくて崩壊🙋‍♀️
-誰か～回収業者さんいませんか～🆘</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>11382</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HTsutTNa8AAVH_h.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2106331262739001771</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="105" customHeight="1">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>46299.40370370371</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>⬅家では𝑵𝒐👙派🙋‍♀️
-君は？</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>8732</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HTvxI7fbgAAaqyN.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2106545168220569778</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="105" customHeight="1">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>46299.88637731481</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>マジでやっっっっっばいことが起きたんですけど…
-今日、スロット打ってたら、店員さんから｢業務妨害だから帰ってくれ！｣って怒られました😖
-全然身に覚えなかったから「なんでですか？」って聞いたら、</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>936</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>286813</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HTySWX0bgAAgKnq.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2106720083087438270</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="105" customHeight="1">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>46300.34648148148</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>⬅不正に学割を利用している23歳
-こんな合法口りにリプしてる君も共犯だけど大丈夫そ？
-ねぇ、一緒に逃避行してくれるよね🥺🚗³₃？
-ちなみに、                                                                                                                                                               
-全部冗談です笑笑
-あ、一生一緒にいたいのは本当😌
-まだ高〇生いけるかな？
-痛いおばさんとか言わんでっ！
-今日からまた1週間始まるから一緒に頑張ろうね💪</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>10810</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HT0mst7bIAAO0hG.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2106886817782149239</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="105" customHeight="1">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>46300.81396990741</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>🥧🥧デカすぎて入退勤ゲートに挟まっちゃってやっと退勤なう
-そのぶん2時間分の残業代GETで神👍
-また挟まった時はキミを🥧🥧専門業者さんとして呼んでいいですか？</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>6971</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HT3EY2Fa0AAwqxi.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2107056232506986508</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="105" customHeight="1">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>46301.81674768519</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>ちょっと待って！？やばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばいやばい本当になにが起こってるの！？マジで分からなすぎて頭がこんがらがってる…
-だって急に、</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>7009</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HT8Ou5fagAEmpuv.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2107419626166751706</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="105" customHeight="1">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>46302.80231481481</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>清楚系ぶってる私ですが、、、
-夜のお〇んぽが大好物💕😋😍💕
-〇に入る文字、なんだかわかる？</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>10044</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUBTzGubsAAsI6A.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2107776782749561216</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="105" customHeight="1">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>46303.40835648148</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>昨日スロット打ってる時にやらかした、ちょっとえっちな話なんですけど …さらに表示</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>7746</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUEbEVNa8AA5xJM.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2107996404346220708</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="105" customHeight="1">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>46304.50135416666</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>イーロン・マスクさんへ、
-まずはこんにちは。
-今日は言っておきたい事があってご連絡しました。
-勝手に私のポストを見えなくしないでください。
-ドウテイですか？
-あんなのでおっきくなってたら私の本気みたら破裂しちゃうんじゃないですか？
-マジでいい加減にしてください。
-ちなみに、           
-こういうえちな写真見逃したくない人は通知ONにしてすぐに駆けつけてくれたら嬉しい！
-見えなくなったら消しちゃうからねん😖</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>8541</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUKCkTLawAAJxca.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2108392493616398501</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="105" customHeight="1">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>46305.35016203704</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>ちょっと聞いてみたいんだけど、 
-あなたはどんな女の子が好き? ↓
-①ポジティブのあちゃん😉
-②ネガティブのあちゃん🥺
-③どんなのあも受け入れるよ😎✨ｷﾗｰﾝ
-答えは... わかってるよね？
-あっ、                                                                                                        
-おはのあ😌</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>10355</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUObjXGbwAAxHrR.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2108700090961653945</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="105" customHeight="1">
-      <c r="A57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>46306.4109837963</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>⚠️緊急事態⚠️
-ちょっと今すぐ答えて欲しいんですけど、君の私への気持ちって
-①好き              ②めちゃ好き
-③まぁ好き     ④𝑳‌𝑶‌𝑽‌𝑬 𝑭𝑶𝑹𝑬𝑽𝑬𝑹…
-どれですか🥺❔
-答えてくれないと不安で夜しか眠れません😖🤞</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>19539</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUT5Dzwa4AAA9sF.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2109084521736114593</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="105" customHeight="1">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>46307.30584490741</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>出社はいつもギリなのにパチ屋の並びは余裕で間に合う限界OLはこちら🙋‍♀️
-3連休の締めはやっぱこれ。
-みんなは何するのー？
-リプで教えて🫶</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>13556</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUYfUhwbwAAxX-k.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2109408809139732543</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="105" customHeight="1">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3" t="n">
-        <v>46307.93532407407</v>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>さっきスロット打ってた時に、隣の知らない人から急に「彼氏いますか？」って聞かれて、
-距離感やばと思いながら「いないですけど…」って答えたら、
-「あ、やっぱり」って言われて、
-（やっぱりって何？？？？）ってイラッとしたけど気になりすぎてなんでか聞いたら、
-笑いながら</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>711</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>802343</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUbu6a-akAAqhcx.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2109636924218671481</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="105" customHeight="1">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="n">
-        <v>46308.34414351852</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>なんつってる間に会社っすよ(笑)
-あ～あ、限界OLの辛いとこね、これ
-鬱でも会社きたから、
-君からの「頑張れ！」ってリプで
-今日も乗り切りたい😭
-まってる</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>19780</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUd1y29bIAACYT8.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2109785074057240893</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="105" customHeight="1">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="3" t="n">
-        <v>46308.48159722222</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>元彼からのLINEなんだけど、ホント最低の別れ方した相手だし返したくない…</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>15845</v>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUejG_hbsAA4dNj.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2109834886614069392</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="105" customHeight="1">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>46308.8287037037</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>男ってマッッッッジで異常なくらい
-元カノが永遠に自分のことを好きだと思い込んでいるよね。
-付き合ってた頃は私のこと雑に扱ってたくせに、別れた途端に会いたいとか言ってきて断ったらこれ。
-こんなこと言う人と一緒にいるくらいなら生涯独り身の方が幸せなんだけど。
-でも正直言うと、          
-これが来てから怒り通り越して悔しすぎて、仕事中なのにずっと泣いてた。
-そして今はすごく悲しいよ。
-昔好きだった人に、ヤリたいだけで連絡されて断ったらこんな言葉を投げつけられて。
-前職の事もバカにされて。
-まだ泣けてくる。
-私が欲しかったのって、お金でも高級なデートでもなくて、ただ安心して甘えられる関係だったんだよね。
-本当は好きな人の前くらい弱い女でいたいよ。
-次はちゃんと、お互いを大切にできる恋愛がしたいな。
-男性目線で聞きたいんだけど、
-別れた女性にもずっと自分を好きでいてほしいものなの？</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>4478</v>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUgWC7KbMAAU0US.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2109960675384836331</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="105" customHeight="1">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>46308.8966087963</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>まじで情緒どうなってる！？ってなると思うんだけど、
-スロッターとして777は絶対に逃せないので、到達したらその瞬間スクショ撮って私にDM送ってほしいです🥺
-それまでプロフ監視しててほしいな。
-777のスクショを送ってもらえたら…                                                               
-プレゼント企画でもやろうかな…！
-全員で協力してラッキー7スクショしてほしいです😖！</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>2576</v>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUgsbQQbUAAfX76.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2109985279897690267</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="105" customHeight="1">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>46309.32993055556</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>ポスト</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>男性だけに答えて欲しいんですけど
-好きになった女性に
-誰にも言えない過去があって
-自分の知らない所で
-色んな男性と関係してたと知ったら
-それでも愛せますか？
-① 過去なんて関係ない
-② 嫉妬するけど受け入れる
-③ 内容しだいで受け入れる
-④ どんな理由でも無理
-綺麗事抜きで答えてほしいです</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>1129</v>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/media/HUi7KkcbkAAW5ku.jpg?name=orig</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/noa_dayo2004/status/2110142311321813229</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L64"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>